--- a/research/traditional_assets/database/data/indonesia/indonesia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06634999999999999</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.0221</v>
+        <v>0.1153</v>
       </c>
       <c r="F2">
-        <v>-0.05899999999999997</v>
+        <v>0.175</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80.14400000000001</v>
+        <v>118.27</v>
       </c>
       <c r="L2">
-        <v>0.05451231125017005</v>
+        <v>0.07713428552794627</v>
       </c>
       <c r="M2">
-        <v>23.764</v>
+        <v>56.374</v>
       </c>
       <c r="N2">
-        <v>0.001941027525933186</v>
+        <v>0.01188723009446694</v>
       </c>
       <c r="O2">
-        <v>0.2965162707127171</v>
+        <v>0.4766551111862687</v>
       </c>
       <c r="P2">
-        <v>22.264</v>
+        <v>56.374</v>
       </c>
       <c r="Q2">
-        <v>0.001818508535489668</v>
+        <v>0.01188723009446694</v>
       </c>
       <c r="R2">
-        <v>0.2777999600718706</v>
+        <v>0.4766551111862687</v>
       </c>
       <c r="S2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.06312068675307188</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>4443.9</v>
+        <v>1633.1</v>
       </c>
       <c r="V2">
-        <v>0.3629747610879686</v>
+        <v>0.3443615047233468</v>
       </c>
       <c r="W2">
-        <v>0.003025830258302583</v>
+        <v>0.01173881144534116</v>
       </c>
       <c r="X2">
-        <v>0.0563536230931226</v>
+        <v>0.07675910067359785</v>
       </c>
       <c r="Y2">
-        <v>-0.05332779283482002</v>
+        <v>-0.0650202892282567</v>
       </c>
       <c r="Z2">
-        <v>0.3090298644089956</v>
+        <v>0.2746881162142306</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05436822391966365</v>
+        <v>0.07531065131900982</v>
       </c>
       <c r="AC2">
-        <v>-0.05436822391966365</v>
+        <v>-0.07531065131900982</v>
       </c>
       <c r="AD2">
-        <v>4458.197</v>
+        <v>4195.842</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4458.197</v>
+        <v>4195.842</v>
       </c>
       <c r="AG2">
-        <v>14.29700000000048</v>
+        <v>2562.742</v>
       </c>
       <c r="AH2">
-        <v>0.2669387709156416</v>
+        <v>0.4694258669657859</v>
       </c>
       <c r="AI2">
-        <v>0.4535852149556044</v>
+        <v>0.4744097412786615</v>
       </c>
       <c r="AJ2">
-        <v>0.001166407242967228</v>
+        <v>0.3508134407243555</v>
       </c>
       <c r="AK2">
-        <v>0.002655018285400905</v>
+        <v>0.3553815001632173</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Bank Woori Saudara Indonesia 1906 Tbk (IDX:SDRA)</t>
+          <t>PT. Bank Pembangunan Daerah Banten, Tbk (IDX:BEKS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0712</v>
-      </c>
-      <c r="E3">
-        <v>0.15</v>
+        <v>0.288</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +728,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>39.4</v>
+        <v>-16.1</v>
       </c>
       <c r="L3">
-        <v>0.3799421407907425</v>
+        <v>-0.8655913978494624</v>
       </c>
       <c r="M3">
-        <v>4.61</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01374068554396423</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.117005076142132</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>4.61</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01374068554396423</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.117005076142132</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>122.4</v>
+        <v>58</v>
       </c>
       <c r="V3">
-        <v>0.3648286140089419</v>
+        <v>0.3493975903614458</v>
       </c>
       <c r="W3">
-        <v>0.08199791883454734</v>
+        <v>-0.1647901740020471</v>
       </c>
       <c r="X3">
-        <v>0.09951357845524422</v>
+        <v>0.07221743341161606</v>
       </c>
       <c r="Y3">
-        <v>-0.01751565962069689</v>
+        <v>-0.2370076074136632</v>
       </c>
       <c r="Z3">
-        <v>0.1108972302427548</v>
+        <v>1.878787878787878</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05234455621480311</v>
+        <v>0.07220572491566835</v>
       </c>
       <c r="AC3">
-        <v>-0.05234455621480311</v>
+        <v>-0.07220572491566835</v>
       </c>
       <c r="AD3">
-        <v>594</v>
+        <v>0.802</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>594</v>
+        <v>0.802</v>
       </c>
       <c r="AG3">
-        <v>471.6</v>
+        <v>-57.198</v>
       </c>
       <c r="AH3">
-        <v>0.6390532544378699</v>
+        <v>0.004808095826189135</v>
       </c>
       <c r="AI3">
-        <v>0.4904227212681638</v>
+        <v>0.006872204418090521</v>
       </c>
       <c r="AJ3">
-        <v>0.5843142113740553</v>
+        <v>-0.525707248028529</v>
       </c>
       <c r="AK3">
-        <v>0.4331373989713446</v>
+        <v>-0.9743790671527375</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Bank Tabungan Negara (Persero) Tbk (IDX:BBTN)</t>
+          <t>PT Bank BTPN Syariah Tbk (IDX:BTPS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,13 +829,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.064</v>
+        <v>0.13</v>
       </c>
       <c r="E4">
-        <v>-0.0235</v>
-      </c>
-      <c r="F4">
-        <v>-0.569</v>
+        <v>0.229</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,82 +847,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>139.9</v>
+        <v>111.4</v>
       </c>
       <c r="L4">
-        <v>0.1848817232721026</v>
+        <v>0.4181681681681682</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>29.6</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0215225768923144</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2657091561938958</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>29.6</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0215225768923144</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2657091561938958</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>1704.7</v>
+        <v>184.9</v>
       </c>
       <c r="V4">
-        <v>1.329304429195259</v>
+        <v>0.1344433941685451</v>
       </c>
       <c r="W4">
-        <v>0.1180889676711404</v>
+        <v>0.236769394261424</v>
       </c>
       <c r="X4">
-        <v>0.112478207094734</v>
+        <v>0.07231319228960792</v>
       </c>
       <c r="Y4">
-        <v>0.005610760576406401</v>
+        <v>0.1644562019718161</v>
       </c>
       <c r="Z4">
-        <v>0.3559768546831633</v>
+        <v>0.9349664829958234</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05425533656960244</v>
+        <v>0.0722662440604029</v>
       </c>
       <c r="AC4">
-        <v>-0.05425533656960244</v>
+        <v>-0.0722662440604029</v>
       </c>
       <c r="AD4">
-        <v>2922.2</v>
+        <v>11.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2922.2</v>
+        <v>11.3</v>
       </c>
       <c r="AG4">
-        <v>1217.5</v>
+        <v>-173.6</v>
       </c>
       <c r="AH4">
-        <v>0.6950007135042572</v>
+        <v>0.008149430261070244</v>
       </c>
       <c r="AI4">
-        <v>0.6698299179388437</v>
+        <v>0.02118088097469541</v>
       </c>
       <c r="AJ4">
-        <v>0.4870194807792311</v>
+        <v>-0.1444620121494549</v>
       </c>
       <c r="AK4">
-        <v>0.4580683998645547</v>
+        <v>-0.4979919678714859</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Bank China Construction Bank Indonesia Tbk (IDX:MCOR)</t>
+          <t>PT Bank Oke Indonesia Tbk (IDX:DNAR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +951,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0687</v>
+        <v>0.292</v>
       </c>
       <c r="E5">
-        <v>-0.018</v>
+        <v>0.0746</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>5.59</v>
+        <v>1.08</v>
       </c>
       <c r="L5">
-        <v>0.1247767857142857</v>
+        <v>0.05837837837837838</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,55 +996,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>244</v>
+        <v>26.2</v>
       </c>
       <c r="V5">
-        <v>0.7924650860669049</v>
+        <v>0.1725955204216074</v>
       </c>
       <c r="W5">
-        <v>0.01381270076599951</v>
+        <v>0.00608793686583991</v>
       </c>
       <c r="X5">
-        <v>0.05687420507811423</v>
+        <v>0.07337406355551557</v>
       </c>
       <c r="Y5">
-        <v>-0.04306150431211472</v>
+        <v>-0.06728612668967565</v>
       </c>
       <c r="Z5">
-        <v>1.313782991202347</v>
+        <v>0.1292097948008772</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05433525795839202</v>
+        <v>0.07321703292165896</v>
       </c>
       <c r="AC5">
-        <v>-0.05433525795839202</v>
+        <v>-0.07321703292165896</v>
       </c>
       <c r="AD5">
-        <v>30.5</v>
+        <v>6.94</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>30.5</v>
+        <v>6.94</v>
       </c>
       <c r="AG5">
-        <v>-213.5</v>
+        <v>-19.26</v>
       </c>
       <c r="AH5">
-        <v>0.09013002364066194</v>
+        <v>0.04371928940405695</v>
       </c>
       <c r="AI5">
-        <v>0.0669887985943334</v>
+        <v>0.03347159255329411</v>
       </c>
       <c r="AJ5">
-        <v>-2.261652542372882</v>
+        <v>-0.1453146220009053</v>
       </c>
       <c r="AK5">
-        <v>-1.010411736867014</v>
+        <v>-0.1063265982113282</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1061,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Bank BTPN Syariah Tbk (IDX:BTPS)</t>
+          <t>PT Bank Neo Commerce Tbk (IDX:BBYB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,13 +1070,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.156</v>
-      </c>
-      <c r="E6">
-        <v>0.34</v>
-      </c>
-      <c r="F6">
-        <v>0.451</v>
+        <v>0.198</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,85 +1085,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>101.1</v>
+        <v>-86.90000000000001</v>
       </c>
       <c r="L6">
-        <v>0.4047237790232185</v>
+        <v>-1.984018264840183</v>
       </c>
       <c r="M6">
-        <v>16.9</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.008756476683937824</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.1671612265084075</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>16.9</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.008756476683937824</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1671612265084075</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>191.3</v>
+        <v>16.8</v>
       </c>
       <c r="V6">
-        <v>0.09911917098445597</v>
+        <v>0.04319876574955002</v>
       </c>
       <c r="W6">
-        <v>0.2714093959731543</v>
+        <v>-1.122739018087855</v>
       </c>
       <c r="X6">
-        <v>0.0544229057100904</v>
+        <v>0.07269687089247928</v>
       </c>
       <c r="Y6">
-        <v>0.2169864902630639</v>
+        <v>-1.195435888980335</v>
       </c>
       <c r="Z6">
-        <v>0.9217712177121772</v>
+        <v>1.649096385542169</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05434677569200181</v>
+        <v>0.0732253884853528</v>
       </c>
       <c r="AC6">
-        <v>-0.05434677569200181</v>
+        <v>-0.0732253884853528</v>
       </c>
       <c r="AD6">
-        <v>5.73</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>5.73</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AG6">
-        <v>-185.57</v>
+        <v>-8.33</v>
       </c>
       <c r="AH6">
-        <v>0.002960123570952561</v>
+        <v>0.02131514709213076</v>
       </c>
       <c r="AI6">
-        <v>0.01203200134388846</v>
+        <v>0.05413178245030997</v>
       </c>
       <c r="AJ6">
-        <v>-0.1063785878481796</v>
+        <v>-0.02188822030112726</v>
       </c>
       <c r="AK6">
-        <v>-0.6512827712069633</v>
+        <v>-0.05964058137037303</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1177,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT Bank MNC Internasional Tbk (IDX:BABP)</t>
+          <t>PT Bank Raya Indonesia Tbk (IDX:AGRO)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1200,29 +1185,8 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0366</v>
-      </c>
-      <c r="E7">
-        <v>0.102</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="L7">
-        <v>0.02619444444444444</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1231,7 +1195,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1240,61 +1204,61 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>134.9</v>
+        <v>27.4</v>
       </c>
       <c r="V7">
-        <v>0.3558427855447112</v>
+        <v>0.04659071586464886</v>
       </c>
       <c r="W7">
-        <v>0.009182083739045764</v>
+        <v>-0.440158820192853</v>
       </c>
       <c r="X7">
-        <v>0.05434736869033779</v>
+        <v>0.0739759712603444</v>
       </c>
       <c r="Y7">
-        <v>-0.04516528495129202</v>
+        <v>-0.5141347914531974</v>
       </c>
       <c r="Z7">
-        <v>1.706161137440758</v>
+        <v>0</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05434718143816177</v>
+        <v>0.07350984567571521</v>
       </c>
       <c r="AC7">
-        <v>-0.05434718143816177</v>
+        <v>-0.07350984567571521</v>
       </c>
       <c r="AD7">
-        <v>0.003</v>
+        <v>39.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.003</v>
+        <v>39.4</v>
       </c>
       <c r="AG7">
-        <v>-134.897</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>7.913416670403557e-06</v>
+        <v>0.06278884462151395</v>
       </c>
       <c r="AI7">
-        <v>2.255588219814591e-05</v>
+        <v>0.2002032520325203</v>
       </c>
       <c r="AJ7">
-        <v>-0.5523969812000672</v>
+        <v>0.01999666722212964</v>
       </c>
       <c r="AK7">
-        <v>71.11070110701034</v>
+        <v>0.07083825265643447</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1275,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P.T. Bank Bumi Arta Tbk (IDX:BNBA)</t>
+          <t>PT Bank Bumi Arta Tbk (IDX:BNBA)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,10 +1284,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0181</v>
+        <v>-0.0168</v>
       </c>
       <c r="E8">
-        <v>-0.0221</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,28 +1302,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3.99</v>
+        <v>3.63</v>
       </c>
       <c r="L8">
-        <v>0.1882075471698113</v>
+        <v>0.1762135922330097</v>
       </c>
       <c r="M8">
-        <v>0.647</v>
+        <v>0.774</v>
       </c>
       <c r="N8">
-        <v>0.001038523274478331</v>
+        <v>0.004716636197440585</v>
       </c>
       <c r="O8">
-        <v>0.1621553884711779</v>
+        <v>0.2132231404958678</v>
       </c>
       <c r="P8">
-        <v>0.647</v>
+        <v>0.774</v>
       </c>
       <c r="Q8">
-        <v>0.001038523274478331</v>
+        <v>0.004716636197440585</v>
       </c>
       <c r="R8">
-        <v>0.1621553884711779</v>
+        <v>0.2132231404958678</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1368,55 +1332,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>24.7</v>
+        <v>32.3</v>
       </c>
       <c r="V8">
-        <v>0.03964686998394863</v>
+        <v>0.1968312004875076</v>
       </c>
       <c r="W8">
-        <v>0.03958333333333334</v>
+        <v>0.03206713780918728</v>
       </c>
       <c r="X8">
-        <v>0.0543535547138994</v>
+        <v>0.07268928658958276</v>
       </c>
       <c r="Y8">
-        <v>-0.01477022138056606</v>
+        <v>-0.04062214878039549</v>
       </c>
       <c r="Z8">
-        <v>-1.709677419354838</v>
+        <v>0.2323587800036095</v>
       </c>
       <c r="AA8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05434854325534558</v>
+        <v>0.07358927515789242</v>
       </c>
       <c r="AC8">
-        <v>-0.05434854325534558</v>
+        <v>-0.07358927515789242</v>
       </c>
       <c r="AD8">
-        <v>0.156</v>
+        <v>3.53</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.156</v>
+        <v>3.53</v>
       </c>
       <c r="AG8">
-        <v>-24.544</v>
+        <v>-28.77</v>
       </c>
       <c r="AH8">
-        <v>0.000250338599002497</v>
+        <v>0.0210582831235459</v>
       </c>
       <c r="AI8">
-        <v>0.001376195349165461</v>
+        <v>0.02321910149312635</v>
       </c>
       <c r="AJ8">
-        <v>-0.04101220474019811</v>
+        <v>-0.2125914431389936</v>
       </c>
       <c r="AK8">
-        <v>-0.276845334777116</v>
+        <v>-0.2402906539714357</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1433,7 +1397,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT Bank Neo Commerce Tbk (IDX:BBYB)</t>
+          <t>PT Bank China Construction Bank Indonesia Tbk (IDX:MCOR)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1442,7 +1406,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.09029999999999999</v>
+        <v>0.0225</v>
+      </c>
+      <c r="E9">
+        <v>0.6920000000000001</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1457,85 +1424,82 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-17.7</v>
+        <v>6.64</v>
       </c>
       <c r="L9">
-        <v>-0.7499999999999999</v>
+        <v>0.1596153846153846</v>
       </c>
       <c r="M9">
-        <v>0.107</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>6.231073841136733e-05</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0.006045197740112995</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>0.107</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>6.231073841136733e-05</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0.006045197740112995</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>54.8</v>
+        <v>53.1</v>
       </c>
       <c r="V9">
-        <v>0.0319124155602143</v>
+        <v>0.2735703245749614</v>
       </c>
       <c r="W9">
-        <v>-0.2375838926174497</v>
+        <v>0.01563088512241054</v>
       </c>
       <c r="X9">
-        <v>0.05440599642290112</v>
+        <v>0.07675910067359785</v>
       </c>
       <c r="Y9">
-        <v>-0.2919898890403508</v>
+        <v>-0.06112821555118731</v>
       </c>
       <c r="Z9">
-        <v>0.3913180453995258</v>
+        <v>0.2101010101010101</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05435141919402919</v>
+        <v>0.07531065131900982</v>
       </c>
       <c r="AC9">
-        <v>-0.05435141919402919</v>
+        <v>-0.07531065131900982</v>
       </c>
       <c r="AD9">
-        <v>3.96</v>
+        <v>32.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>3.96</v>
+        <v>32.1</v>
       </c>
       <c r="AG9">
-        <v>-50.84</v>
+        <v>-21</v>
       </c>
       <c r="AH9">
-        <v>0.002300773896674336</v>
+        <v>0.1419098143236074</v>
       </c>
       <c r="AI9">
-        <v>0.04867256637168142</v>
+        <v>0.07359009628610728</v>
       </c>
       <c r="AJ9">
-        <v>-0.03050961376893348</v>
+        <v>-0.121317157712305</v>
       </c>
       <c r="AK9">
-        <v>-1.914156626506023</v>
+        <v>-0.05481597494126859</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1552,7 +1516,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PT Bank Sinarmas Tbk (IDX:BSIM)</t>
+          <t>PT Bank Tabungan Negara (Persero) Tbk (IDX:BBTN)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1561,10 +1525,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0269</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="E10">
-        <v>-0.178</v>
+        <v>0.00869</v>
+      </c>
+      <c r="F10">
+        <v>0.175</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1579,82 +1546,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>8.869999999999999</v>
+        <v>205.9</v>
       </c>
       <c r="L10">
-        <v>0.06786534047436878</v>
+        <v>0.2356374456397345</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>15.6</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.01704918032786885</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.07576493443419136</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>15.6</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.01704918032786885</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.07576493443419136</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>639.8</v>
+        <v>718.9</v>
       </c>
       <c r="V10">
-        <v>0.5298111957601855</v>
+        <v>0.7856830601092896</v>
       </c>
       <c r="W10">
-        <v>0.02291397571686902</v>
+        <v>0.1429464037767287</v>
       </c>
       <c r="X10">
-        <v>0.05447750861626245</v>
+        <v>0.1565602472911439</v>
       </c>
       <c r="Y10">
-        <v>-0.03156353289939343</v>
+        <v>-0.01361384351441519</v>
       </c>
       <c r="Z10">
-        <v>0.8548070634401567</v>
+        <v>0.3287557846420106</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0543565620347779</v>
+        <v>0.08422823668299195</v>
       </c>
       <c r="AC10">
-        <v>-0.0543565620347779</v>
+        <v>-0.08422823668299195</v>
       </c>
       <c r="AD10">
-        <v>6.17</v>
+        <v>2732.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>6.17</v>
+        <v>2732.5</v>
       </c>
       <c r="AG10">
-        <v>-633.63</v>
+        <v>2013.6</v>
       </c>
       <c r="AH10">
-        <v>0.005083335393031629</v>
+        <v>0.7491432488005483</v>
       </c>
       <c r="AI10">
-        <v>0.01190039925164426</v>
+        <v>0.6583226925578818</v>
       </c>
       <c r="AJ10">
-        <v>-1.103942714776034</v>
+        <v>0.6875640237656218</v>
       </c>
       <c r="AK10">
-        <v>5.22236874639413</v>
+        <v>0.5867474794568448</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1671,7 +1641,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT Bank Ganesha Tbk (IDX:BGTG)</t>
+          <t>PT Victoria Investama Tbk (IDX:VICO)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1680,7 +1650,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0219</v>
+        <v>0.0203</v>
+      </c>
+      <c r="E11">
+        <v>-0.462</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1695,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-0.279</v>
+        <v>1.6</v>
       </c>
       <c r="L11">
-        <v>-0.02657142857142857</v>
+        <v>0.02395209580838323</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1707,7 +1680,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1716,61 +1689,61 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>281.5</v>
+        <v>154.1</v>
       </c>
       <c r="V11">
-        <v>1.474594028287061</v>
+        <v>1.459280303030303</v>
       </c>
       <c r="W11">
-        <v>-0.003618677042801557</v>
+        <v>0.01173881144534116</v>
       </c>
       <c r="X11">
-        <v>0.0546411607805343</v>
+        <v>0.09844063782373881</v>
       </c>
       <c r="Y11">
-        <v>-0.05825983782333585</v>
+        <v>-0.08670182637839766</v>
       </c>
       <c r="Z11">
-        <v>0.2535007242877837</v>
+        <v>0.4570865522125588</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05436822391966365</v>
+        <v>0.08461719012440921</v>
       </c>
       <c r="AC11">
-        <v>-0.05436822391966365</v>
+        <v>-0.08461719012440921</v>
       </c>
       <c r="AD11">
-        <v>2.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AG11">
-        <v>-279.3</v>
+        <v>-55.69999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.01139306059036769</v>
+        <v>0.4823529411764706</v>
       </c>
       <c r="AI11">
-        <v>0.02682926829268293</v>
+        <v>0.2900088417329797</v>
       </c>
       <c r="AJ11">
-        <v>3.159502262443439</v>
+        <v>-1.116232464929859</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>-0.3007559395248379</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1787,7 +1760,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PT Bank Rakyat Indonesia Agroniaga Tbk (IDX:AGRO)</t>
+          <t>PT Bank Victoria International Tbk (IDX:BVIC)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1795,23 +1768,26 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D12">
+        <v>-0.0479</v>
+      </c>
       <c r="G12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>-127.8</v>
+        <v>-2.85</v>
       </c>
       <c r="L12">
-        <v>1.243190661478599</v>
+        <v>-0.08482142857142858</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1835,55 +1811,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>30.7</v>
+        <v>50.1</v>
       </c>
       <c r="V12">
-        <v>0.01075947148915291</v>
+        <v>0.561030235162374</v>
       </c>
       <c r="W12">
-        <v>-0.4506346967559943</v>
+        <v>-0.01503164556962025</v>
       </c>
       <c r="X12">
-        <v>0.05485231951306636</v>
+        <v>0.1041707952444622</v>
       </c>
       <c r="Y12">
-        <v>-0.5054870162690607</v>
+        <v>-0.1192024408140824</v>
       </c>
       <c r="Z12">
-        <v>-1.181609195402298</v>
+        <v>0.1321793863099922</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.05438305434596933</v>
+        <v>0.08589399806603105</v>
       </c>
       <c r="AC12">
-        <v>-0.05438305434596933</v>
+        <v>-0.08589399806603105</v>
       </c>
       <c r="AD12">
-        <v>56.5</v>
+        <v>101.3</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>56.5</v>
+        <v>101.3</v>
       </c>
       <c r="AG12">
-        <v>25.8</v>
+        <v>51.2</v>
       </c>
       <c r="AH12">
-        <v>0.01941714207162004</v>
+        <v>0.531479538300105</v>
       </c>
       <c r="AI12">
-        <v>0.2426975945017182</v>
+        <v>0.3159700561447286</v>
       </c>
       <c r="AJ12">
-        <v>0.008961133687610711</v>
+        <v>0.3644128113879003</v>
       </c>
       <c r="AK12">
-        <v>0.1276595744680851</v>
+        <v>0.189279112754159</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1900,7 +1876,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PT Bank Oke Indonesia Tbk (IDX:DNAR)</t>
+          <t>PT Bank Woori Saudara Indonesia 1906 Tbk (IDX:SDRA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1909,10 +1885,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.303</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E13">
-        <v>-0.138</v>
+        <v>0.156</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1927,85 +1903,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.41</v>
+        <v>53.1</v>
       </c>
       <c r="L13">
-        <v>0.02091836734693877</v>
+        <v>0.4187697160883281</v>
       </c>
       <c r="M13">
-        <v>1.5</v>
+        <v>10.4</v>
       </c>
       <c r="N13">
-        <v>0.005368647100930566</v>
+        <v>0.03326935380678183</v>
       </c>
       <c r="O13">
-        <v>3.658536585365854</v>
+        <v>0.1958568738229755</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>10.4</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.03326935380678183</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.1958568738229755</v>
       </c>
       <c r="S13">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>34.9</v>
+        <v>89</v>
       </c>
       <c r="V13">
-        <v>0.1249105225483178</v>
+        <v>0.2847088931541906</v>
       </c>
       <c r="W13">
-        <v>0.003025830258302583</v>
+        <v>0.08603370058327932</v>
       </c>
       <c r="X13">
-        <v>0.05440907170280087</v>
+        <v>0.1403861716242006</v>
       </c>
       <c r="Y13">
-        <v>-0.05138324144449829</v>
+        <v>-0.05435247104092124</v>
       </c>
       <c r="Z13">
-        <v>0.1648402479331893</v>
+        <v>0.1286525974025974</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05438603199949161</v>
+        <v>0.08817535238004406</v>
       </c>
       <c r="AC13">
-        <v>-0.05438603199949161</v>
+        <v>-0.08817535238004406</v>
       </c>
       <c r="AD13">
-        <v>0.678</v>
+        <v>754.8</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.678</v>
+        <v>754.8</v>
       </c>
       <c r="AG13">
-        <v>-34.222</v>
+        <v>665.8</v>
       </c>
       <c r="AH13">
-        <v>0.002420754218467713</v>
+        <v>0.7071388420460932</v>
       </c>
       <c r="AI13">
-        <v>0.00380732038769528</v>
+        <v>0.543021582733813</v>
       </c>
       <c r="AJ13">
-        <v>-0.139580223347935</v>
+        <v>0.6804987735077678</v>
       </c>
       <c r="AK13">
-        <v>-0.2390171674419254</v>
+        <v>0.5117601844734819</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2022,7 +1998,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PT Bank Artha Graha Internasional Tbk (IDX:INPC)</t>
+          <t>PT Bank QNB Indonesia Tbk (IDX:BKSW)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2030,29 +2006,8 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>-0.09859999999999999</v>
-      </c>
-      <c r="E14">
-        <v>-0.174</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
       <c r="K14">
-        <v>1.59</v>
-      </c>
-      <c r="L14">
-        <v>0.03680555555555556</v>
+        <v>-87.2</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2061,7 +2016,7 @@
         <v>-0</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2070,61 +2025,61 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>345.9</v>
+        <v>131.2</v>
       </c>
       <c r="V14">
-        <v>1.943258426966292</v>
+        <v>0.9835082458770613</v>
       </c>
       <c r="W14">
-        <v>0.007168620378719568</v>
+        <v>-0.3560636994691711</v>
       </c>
       <c r="X14">
-        <v>0.0563536230931226</v>
+        <v>0.08601302667163108</v>
       </c>
       <c r="Y14">
-        <v>-0.04918500271440303</v>
+        <v>-0.4420767261408022</v>
       </c>
       <c r="Z14">
-        <v>-0.8074766355140187</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05448193429363056</v>
+        <v>0.1074997460531805</v>
       </c>
       <c r="AC14">
-        <v>-0.05448193429363056</v>
+        <v>-0.1074997460531805</v>
       </c>
       <c r="AD14">
-        <v>14</v>
+        <v>65.7</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>14</v>
+        <v>65.7</v>
       </c>
       <c r="AG14">
-        <v>-331.9</v>
+        <v>-65.49999999999999</v>
       </c>
       <c r="AH14">
-        <v>0.07291666666666667</v>
+        <v>0.3299849321948769</v>
       </c>
       <c r="AI14">
-        <v>0.05263157894736842</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="AJ14">
-        <v>2.156595191682911</v>
+        <v>-0.9646539027982322</v>
       </c>
       <c r="AK14">
-        <v>4.153942428035045</v>
+        <v>-0.3734321550741161</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2141,7 +2096,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PT. Bank Pembangunan Daerah Banten, Tbk (IDX:BEKS)</t>
+          <t>PT Bank IBK Indonesia Tbk (IDX:AGRS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2150,7 +2105,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.207</v>
+        <v>0.213</v>
+      </c>
+      <c r="E15">
+        <v>1.057</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2165,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>-22.1</v>
+        <v>5.57</v>
       </c>
       <c r="L15">
-        <v>-10.52380952380952</v>
+        <v>0.2442982456140351</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2177,7 +2135,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2186,530 +2144,66 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>101.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V15">
-        <v>0.6107423053711527</v>
+        <v>0.5758533501896334</v>
       </c>
       <c r="W15">
-        <v>-0.7978339350180507</v>
+        <v>0.0400431344356578</v>
       </c>
       <c r="X15">
-        <v>0.05641018928019378</v>
+        <v>0.1329853972474829</v>
       </c>
       <c r="Y15">
-        <v>-0.8542441242982445</v>
+        <v>-0.09294226281182508</v>
       </c>
       <c r="Z15">
-        <v>0.02771179730799683</v>
+        <v>0.06490179333902649</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.05448544940620971</v>
+        <v>0.1087493128012946</v>
       </c>
       <c r="AC15">
-        <v>-0.05448544940620971</v>
+        <v>-0.1087493128012946</v>
       </c>
       <c r="AD15">
-        <v>13.4</v>
+        <v>340.6</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>13.4</v>
+        <v>340.6</v>
       </c>
       <c r="AG15">
-        <v>-87.8</v>
+        <v>249.5</v>
       </c>
       <c r="AH15">
-        <v>0.07481853713009493</v>
+        <v>0.6828388131515638</v>
       </c>
       <c r="AI15">
-        <v>0.1206120612061206</v>
+        <v>0.6329678498420368</v>
       </c>
       <c r="AJ15">
-        <v>-1.127086007702182</v>
+        <v>0.6119695854795193</v>
       </c>
       <c r="AK15">
-        <v>-8.868686868686863</v>
+        <v>0.5581655480984341</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PT Bank QNB Indonesia Tbk (IDX:BKSW)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>-0.121</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>-25.3</v>
-      </c>
-      <c r="L16">
-        <v>-1.246305418719212</v>
-      </c>
-      <c r="M16">
-        <v>-0</v>
-      </c>
-      <c r="N16">
-        <v>-0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>119.9</v>
-      </c>
-      <c r="V16">
-        <v>0.4364761558063342</v>
-      </c>
-      <c r="W16">
-        <v>-0.1097137901127494</v>
-      </c>
-      <c r="X16">
-        <v>0.06442327325360794</v>
-      </c>
-      <c r="Y16">
-        <v>-0.1741370633663573</v>
-      </c>
-      <c r="Z16">
-        <v>0.06695250659630607</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0.05487048104051606</v>
-      </c>
-      <c r="AC16">
-        <v>-0.05487048104051606</v>
-      </c>
-      <c r="AD16">
-        <v>108.5</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>108.5</v>
-      </c>
-      <c r="AG16">
-        <v>-11.40000000000001</v>
-      </c>
-      <c r="AH16">
-        <v>0.2831419624217119</v>
-      </c>
-      <c r="AI16">
-        <v>0.3070175438596491</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.04329661982529437</v>
-      </c>
-      <c r="AK16">
-        <v>-0.04882226980728054</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PT Victoria Investama Tbk (IDX:VICO)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>0.5589999999999999</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>-7.47</v>
-      </c>
-      <c r="L17">
-        <v>-0.136563071297989</v>
-      </c>
-      <c r="M17">
-        <v>-0</v>
-      </c>
-      <c r="N17">
-        <v>-0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>-0</v>
-      </c>
-      <c r="Q17">
-        <v>-0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>163.6</v>
-      </c>
-      <c r="V17">
-        <v>0.9921164342025469</v>
-      </c>
-      <c r="W17">
-        <v>-0.05223776223776223</v>
-      </c>
-      <c r="X17">
-        <v>0.08123468915782669</v>
-      </c>
-      <c r="Y17">
-        <v>-0.1334724513955889</v>
-      </c>
-      <c r="Z17">
-        <v>0.3016150465656137</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0.05529556972803898</v>
-      </c>
-      <c r="AC17">
-        <v>-0.05529556972803898</v>
-      </c>
-      <c r="AD17">
-        <v>173.8</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>173.8</v>
-      </c>
-      <c r="AG17">
-        <v>10.20000000000002</v>
-      </c>
-      <c r="AH17">
-        <v>0.5131384706229701</v>
-      </c>
-      <c r="AI17">
-        <v>0.4358074222668004</v>
-      </c>
-      <c r="AJ17">
-        <v>0.05825242718446611</v>
-      </c>
-      <c r="AK17">
-        <v>0.04336734693877558</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PT Bank Victoria International Tbk (IDX:BVIC)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>0.08939999999999999</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>-15.3</v>
-      </c>
-      <c r="L18">
-        <v>-0.4409221902017291</v>
-      </c>
-      <c r="M18">
-        <v>-0</v>
-      </c>
-      <c r="N18">
-        <v>-0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>-0</v>
-      </c>
-      <c r="Q18">
-        <v>-0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>107.5</v>
-      </c>
-      <c r="V18">
-        <v>0.7248819959541469</v>
-      </c>
-      <c r="W18">
-        <v>-0.08319738988580751</v>
-      </c>
-      <c r="X18">
-        <v>0.08395191607359656</v>
-      </c>
-      <c r="Y18">
-        <v>-0.1671493059594041</v>
-      </c>
-      <c r="Z18">
-        <v>0.1279970490593877</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0.05533993229293641</v>
-      </c>
-      <c r="AC18">
-        <v>-0.05533993229293641</v>
-      </c>
-      <c r="AD18">
-        <v>172.1</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>172.1</v>
-      </c>
-      <c r="AG18">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="AH18">
-        <v>0.5371410736579276</v>
-      </c>
-      <c r="AI18">
-        <v>0.4758086812275366</v>
-      </c>
-      <c r="AJ18">
-        <v>0.3034288398309065</v>
-      </c>
-      <c r="AK18">
-        <v>0.2541306058221872</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PT Bank IBK Indonesia Tbk (IDX:AGRS)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>0.171</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>-5.7</v>
-      </c>
-      <c r="L19">
-        <v>-0.2663551401869159</v>
-      </c>
-      <c r="M19">
-        <v>-0</v>
-      </c>
-      <c r="N19">
-        <v>-0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>-0</v>
-      </c>
-      <c r="Q19">
-        <v>-0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>142.1</v>
-      </c>
-      <c r="V19">
-        <v>0.6928327645051194</v>
-      </c>
-      <c r="W19">
-        <v>-0.04042553191489362</v>
-      </c>
-      <c r="X19">
-        <v>0.0984155543355853</v>
-      </c>
-      <c r="Y19">
-        <v>-0.1388410862504789</v>
-      </c>
-      <c r="Z19">
-        <v>0.1481994459833795</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0.05551776270327659</v>
-      </c>
-      <c r="AC19">
-        <v>-0.05551776270327659</v>
-      </c>
-      <c r="AD19">
-        <v>354.3</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>354.3</v>
-      </c>
-      <c r="AG19">
-        <v>212.2</v>
-      </c>
-      <c r="AH19">
-        <v>0.6333571683947087</v>
-      </c>
-      <c r="AI19">
-        <v>0.718078638021889</v>
-      </c>
-      <c r="AJ19">
-        <v>0.5085070692547329</v>
-      </c>
-      <c r="AK19">
-        <v>0.6040421292342727</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/indonesia/indonesia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09470000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="E2">
-        <v>0.1153</v>
+        <v>0.101</v>
       </c>
       <c r="F2">
-        <v>0.175</v>
+        <v>0.07450000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>118.27</v>
+        <v>354.415</v>
       </c>
       <c r="L2">
-        <v>0.07713428552794627</v>
+        <v>0.2099030483218535</v>
       </c>
       <c r="M2">
-        <v>56.374</v>
+        <v>119.8</v>
       </c>
       <c r="N2">
-        <v>0.01188723009446694</v>
+        <v>0.02441260978542172</v>
       </c>
       <c r="O2">
-        <v>0.4766551111862687</v>
+        <v>0.3380218105892809</v>
       </c>
       <c r="P2">
-        <v>56.374</v>
+        <v>96.2</v>
       </c>
       <c r="Q2">
-        <v>0.01188723009446694</v>
+        <v>0.01960344792452061</v>
       </c>
       <c r="R2">
-        <v>0.4766551111862687</v>
+        <v>0.2714332068337965</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1969949916527546</v>
       </c>
       <c r="U2">
-        <v>1633.1</v>
+        <v>2885.36</v>
       </c>
       <c r="V2">
-        <v>0.3443615047233468</v>
+        <v>0.5879730197868481</v>
       </c>
       <c r="W2">
-        <v>0.01173881144534116</v>
+        <v>0.02317069804204176</v>
       </c>
       <c r="X2">
-        <v>0.07675910067359785</v>
+        <v>0.06384467256436305</v>
       </c>
       <c r="Y2">
-        <v>-0.0650202892282567</v>
+        <v>-0.04067397452232129</v>
       </c>
       <c r="Z2">
-        <v>0.2746881162142306</v>
+        <v>0.2352216925480138</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07531065131900982</v>
+        <v>0.06172067672565322</v>
       </c>
       <c r="AC2">
-        <v>-0.07531065131900982</v>
+        <v>-0.06172067672565322</v>
       </c>
       <c r="AD2">
-        <v>4195.842</v>
+        <v>4584.065000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4195.842</v>
+        <v>4584.065000000001</v>
       </c>
       <c r="AG2">
-        <v>2562.742</v>
+        <v>1698.705</v>
       </c>
       <c r="AH2">
-        <v>0.4694258669657859</v>
+        <v>0.4829721541632842</v>
       </c>
       <c r="AI2">
-        <v>0.4744097412786615</v>
+        <v>0.4184577985725716</v>
       </c>
       <c r="AJ2">
-        <v>0.3508134407243555</v>
+        <v>0.2571455819364351</v>
       </c>
       <c r="AK2">
-        <v>0.3553815001632173</v>
+        <v>0.2105144123316693</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.288</v>
+        <v>0.0708</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>-16.1</v>
+        <v>-8.26</v>
       </c>
       <c r="L3">
-        <v>-0.8655913978494624</v>
+        <v>-0.4489130434782609</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,55 +755,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>58</v>
+        <v>35.8</v>
       </c>
       <c r="V3">
-        <v>0.3493975903614458</v>
+        <v>0.2123368920521945</v>
       </c>
       <c r="W3">
-        <v>-0.1647901740020471</v>
+        <v>-0.07126833477135461</v>
       </c>
       <c r="X3">
-        <v>0.07221743341161606</v>
+        <v>0.06041350547872495</v>
       </c>
       <c r="Y3">
-        <v>-0.2370076074136632</v>
+        <v>-0.1316818402500796</v>
       </c>
       <c r="Z3">
-        <v>1.878787878787878</v>
+        <v>0.3134475827058703</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07220572491566835</v>
+        <v>0.06041350547872495</v>
       </c>
       <c r="AC3">
-        <v>-0.07220572491566835</v>
+        <v>-0.06041350547872495</v>
       </c>
       <c r="AD3">
-        <v>0.802</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.802</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-57.198</v>
+        <v>-35.8</v>
       </c>
       <c r="AH3">
-        <v>0.004808095826189135</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.006872204418090521</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.525707248028529</v>
+        <v>-0.269578313253012</v>
       </c>
       <c r="AK3">
-        <v>-0.9743790671527375</v>
+        <v>-0.5188405797101449</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Bank BTPN Syariah Tbk (IDX:BTPS)</t>
+          <t>PT Bank of India Indonesia Tbk (IDX:BSWD)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,10 +829,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.13</v>
-      </c>
-      <c r="E4">
-        <v>0.229</v>
+        <v>0.0406</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,85 +844,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>111.4</v>
+        <v>2.47</v>
       </c>
       <c r="L4">
-        <v>0.4181681681681682</v>
+        <v>0.3262879788639366</v>
       </c>
       <c r="M4">
-        <v>29.6</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.0215225768923144</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.2657091561938958</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>29.6</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.0215225768923144</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2657091561938958</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>184.9</v>
+        <v>2.96</v>
       </c>
       <c r="V4">
-        <v>0.1344433941685451</v>
+        <v>0.009916247906197655</v>
       </c>
       <c r="W4">
-        <v>0.236769394261424</v>
+        <v>0.01854354354354355</v>
       </c>
       <c r="X4">
-        <v>0.07231319228960792</v>
+        <v>0.06041491741626878</v>
       </c>
       <c r="Y4">
-        <v>0.1644562019718161</v>
+        <v>-0.04187137387272524</v>
       </c>
       <c r="Z4">
-        <v>0.9349664829958234</v>
+        <v>0.1024357239512855</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0722662440604029</v>
+        <v>0.06041470918642859</v>
       </c>
       <c r="AC4">
-        <v>-0.0722662440604029</v>
+        <v>-0.06041470918642859</v>
       </c>
       <c r="AD4">
-        <v>11.3</v>
+        <v>0.025</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>11.3</v>
+        <v>0.025</v>
       </c>
       <c r="AG4">
-        <v>-173.6</v>
+        <v>-2.935</v>
       </c>
       <c r="AH4">
-        <v>0.008149430261070244</v>
+        <v>8.374507997655139e-05</v>
       </c>
       <c r="AI4">
-        <v>0.02118088097469541</v>
+        <v>0.0001150880423523996</v>
       </c>
       <c r="AJ4">
-        <v>-0.1444620121494549</v>
+        <v>-0.009930133811513543</v>
       </c>
       <c r="AK4">
-        <v>-0.4979919678714859</v>
+        <v>-0.01369799080577789</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -942,7 +936,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Bank Oke Indonesia Tbk (IDX:DNAR)</t>
+          <t>PT Bank BTPN Syariah Tbk (IDX:BTPS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -951,10 +945,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.292</v>
+        <v>0.073</v>
       </c>
       <c r="E5">
-        <v>0.0746</v>
+        <v>0.101</v>
+      </c>
+      <c r="F5">
+        <v>0.014</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,82 +966,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1.08</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="L5">
-        <v>0.05837837837837838</v>
+        <v>0.3794354838709677</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>44</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05199716379106594</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.4675876726886292</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>44</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05199716379106594</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.4675876726886292</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>26.2</v>
+        <v>270.6</v>
       </c>
       <c r="V5">
-        <v>0.1725955204216074</v>
+        <v>0.3197825573150556</v>
       </c>
       <c r="W5">
-        <v>0.00608793686583991</v>
+        <v>0.1802681992337165</v>
       </c>
       <c r="X5">
-        <v>0.07337406355551557</v>
+        <v>0.06054320183670163</v>
       </c>
       <c r="Y5">
-        <v>-0.06728612668967565</v>
+        <v>0.1197249973970148</v>
       </c>
       <c r="Z5">
-        <v>0.1292097948008772</v>
+        <v>0.711825487944891</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07321703292165896</v>
+        <v>0.06047273604001465</v>
       </c>
       <c r="AC5">
-        <v>-0.07321703292165896</v>
+        <v>-0.06047273604001465</v>
       </c>
       <c r="AD5">
-        <v>6.94</v>
+        <v>6.51</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>6.94</v>
+        <v>6.51</v>
       </c>
       <c r="AG5">
-        <v>-19.26</v>
+        <v>-264.09</v>
       </c>
       <c r="AH5">
-        <v>0.04371928940405695</v>
+        <v>0.007634483001254823</v>
       </c>
       <c r="AI5">
-        <v>0.03347159255329411</v>
+        <v>0.01145501574844715</v>
       </c>
       <c r="AJ5">
-        <v>-0.1453146220009053</v>
+        <v>-0.453677140059439</v>
       </c>
       <c r="AK5">
-        <v>-0.1063265982113282</v>
+        <v>-0.8870713110073565</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.198</v>
+        <v>0.251</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1085,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-86.90000000000001</v>
+        <v>-48.7</v>
       </c>
       <c r="L6">
-        <v>-1.984018264840183</v>
+        <v>-1.089485458612975</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1112,55 +1112,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>16.8</v>
+        <v>47.7</v>
       </c>
       <c r="V6">
-        <v>0.04319876574955002</v>
+        <v>0.1412078152753108</v>
       </c>
       <c r="W6">
-        <v>-1.122739018087855</v>
+        <v>-0.3290540540540541</v>
       </c>
       <c r="X6">
-        <v>0.07269687089247928</v>
+        <v>0.060606145923649</v>
       </c>
       <c r="Y6">
-        <v>-1.195435888980335</v>
+        <v>-0.3896601999777031</v>
       </c>
       <c r="Z6">
-        <v>1.649096385542169</v>
+        <v>0.3200400945084843</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0732253884853528</v>
+        <v>0.06055237389539854</v>
       </c>
       <c r="AC6">
-        <v>-0.0732253884853528</v>
+        <v>-0.06055237389539854</v>
       </c>
       <c r="AD6">
-        <v>8.470000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>8.470000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="AG6">
-        <v>-8.33</v>
+        <v>-43.84</v>
       </c>
       <c r="AH6">
-        <v>0.02131514709213076</v>
+        <v>0.01129778142012527</v>
       </c>
       <c r="AI6">
-        <v>0.05413178245030997</v>
+        <v>0.01815103921753033</v>
       </c>
       <c r="AJ6">
-        <v>-0.02188822030112726</v>
+        <v>-0.1491359368621581</v>
       </c>
       <c r="AK6">
-        <v>-0.05964058137037303</v>
+        <v>-0.2657613967022309</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT Bank Raya Indonesia Tbk (IDX:AGRO)</t>
+          <t>PT Bank Bumi Arta Tbk (IDX:BNBA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1185,8 +1185,29 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.032</v>
+      </c>
+      <c r="E7">
+        <v>-0.243</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
       <c r="K7">
-        <v>-77.59999999999999</v>
+        <v>1.67</v>
+      </c>
+      <c r="L7">
+        <v>0.08146341463414634</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1195,7 +1216,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1204,61 +1225,61 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>27.4</v>
+        <v>29.7</v>
       </c>
       <c r="V7">
-        <v>0.04659071586464886</v>
+        <v>0.1828817733990148</v>
       </c>
       <c r="W7">
-        <v>-0.440158820192853</v>
+        <v>0.01124579124579124</v>
       </c>
       <c r="X7">
-        <v>0.0739759712603444</v>
+        <v>0.06065122742137334</v>
       </c>
       <c r="Y7">
-        <v>-0.5141347914531974</v>
+        <v>-0.04940543617558209</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>0.1712185751273699</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07350984567571521</v>
+        <v>0.06058441984479755</v>
       </c>
       <c r="AC7">
-        <v>-0.07350984567571521</v>
+        <v>-0.06058441984479755</v>
       </c>
       <c r="AD7">
-        <v>39.4</v>
+        <v>2.29</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>39.4</v>
+        <v>2.29</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>-27.41</v>
       </c>
       <c r="AH7">
-        <v>0.06278884462151395</v>
+        <v>0.01390491225939644</v>
       </c>
       <c r="AI7">
-        <v>0.2002032520325203</v>
+        <v>0.01127023967714947</v>
       </c>
       <c r="AJ7">
-        <v>0.01999666722212964</v>
+        <v>-0.2030520779316986</v>
       </c>
       <c r="AK7">
-        <v>0.07083825265643447</v>
+        <v>-0.1579918150902069</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1275,7 +1296,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT Bank Bumi Arta Tbk (IDX:BNBA)</t>
+          <t>PT Bank QNB Indonesia Tbk (IDX:BKSW)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1284,10 +1305,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0168</v>
-      </c>
-      <c r="E8">
-        <v>-0.06419999999999999</v>
+        <v>0.412</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1302,85 +1320,82 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3.63</v>
+        <v>0.965</v>
       </c>
       <c r="L8">
-        <v>0.1762135922330097</v>
+        <v>0.02863501483679525</v>
       </c>
       <c r="M8">
-        <v>0.774</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.004716636197440585</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.2132231404958678</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>0.774</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.004716636197440585</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.2132231404958678</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>32.3</v>
+        <v>65.7</v>
       </c>
       <c r="V8">
-        <v>0.1968312004875076</v>
+        <v>0.3549432739059968</v>
       </c>
       <c r="W8">
-        <v>0.03206713780918728</v>
+        <v>0.004005811540058115</v>
       </c>
       <c r="X8">
-        <v>0.07268928658958276</v>
+        <v>0.0610674453819289</v>
       </c>
       <c r="Y8">
-        <v>-0.04062214878039549</v>
+        <v>-0.05706163384187079</v>
       </c>
       <c r="Z8">
-        <v>0.2323587800036095</v>
+        <v>0.1921322690992018</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07358927515789242</v>
+        <v>0.06087249275503645</v>
       </c>
       <c r="AC8">
-        <v>-0.07358927515789242</v>
+        <v>-0.06087249275503645</v>
       </c>
       <c r="AD8">
-        <v>3.53</v>
+        <v>7.18</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>3.53</v>
+        <v>7.18</v>
       </c>
       <c r="AG8">
-        <v>-28.77</v>
+        <v>-58.52</v>
       </c>
       <c r="AH8">
-        <v>0.0210582831235459</v>
+        <v>0.0373413771583108</v>
       </c>
       <c r="AI8">
-        <v>0.02321910149312635</v>
+        <v>0.02280233739837398</v>
       </c>
       <c r="AJ8">
-        <v>-0.2125914431389936</v>
+        <v>-0.4623163216937906</v>
       </c>
       <c r="AK8">
-        <v>-0.2402906539714357</v>
+        <v>-0.2348503090135645</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1406,10 +1421,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0225</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="E9">
-        <v>0.6920000000000001</v>
+        <v>0.312</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1424,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>6.64</v>
+        <v>14.4</v>
       </c>
       <c r="L9">
-        <v>0.1596153846153846</v>
+        <v>0.2651933701657459</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1451,55 +1466,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>53.1</v>
+        <v>82.8</v>
       </c>
       <c r="V9">
-        <v>0.2735703245749614</v>
+        <v>0.4305772230889235</v>
       </c>
       <c r="W9">
-        <v>0.01563088512241054</v>
+        <v>0.03563474387527839</v>
       </c>
       <c r="X9">
-        <v>0.07675910067359785</v>
+        <v>0.06309614275780039</v>
       </c>
       <c r="Y9">
-        <v>-0.06112821555118731</v>
+        <v>-0.02746139888252199</v>
       </c>
       <c r="Z9">
-        <v>0.2101010101010101</v>
+        <v>0.1465191581219644</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07531065131900982</v>
+        <v>0.06147857406056692</v>
       </c>
       <c r="AC9">
-        <v>-0.07531065131900982</v>
+        <v>-0.06147857406056692</v>
       </c>
       <c r="AD9">
-        <v>32.1</v>
+        <v>30.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>32.1</v>
+        <v>30.6</v>
       </c>
       <c r="AG9">
-        <v>-21</v>
+        <v>-52.2</v>
       </c>
       <c r="AH9">
-        <v>0.1419098143236074</v>
+        <v>0.1372812920592194</v>
       </c>
       <c r="AI9">
-        <v>0.07359009628610728</v>
+        <v>0.06905890318212593</v>
       </c>
       <c r="AJ9">
-        <v>-0.121317157712305</v>
+        <v>-0.3725910064239828</v>
       </c>
       <c r="AK9">
-        <v>-0.05481597494126859</v>
+        <v>-0.1448792672772689</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1516,7 +1531,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PT Bank Tabungan Negara (Persero) Tbk (IDX:BBTN)</t>
+          <t>PT Bank Raya Indonesia Tbk (IDX:AGRO)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1525,13 +1540,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.06150000000000001</v>
-      </c>
-      <c r="E10">
-        <v>0.00869</v>
-      </c>
-      <c r="F10">
-        <v>0.175</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1546,85 +1555,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>205.9</v>
+        <v>-0.41</v>
       </c>
       <c r="L10">
-        <v>0.2356374456397345</v>
+        <v>-0.00823293172690763</v>
       </c>
       <c r="M10">
-        <v>15.6</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.01704918032786885</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.07576493443419136</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>15.6</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.01704918032786885</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.07576493443419136</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>718.9</v>
+        <v>28.2</v>
       </c>
       <c r="V10">
-        <v>0.7856830601092896</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="W10">
-        <v>0.1429464037767287</v>
+        <v>-0.002604828462515883</v>
       </c>
       <c r="X10">
-        <v>0.1565602472911439</v>
+        <v>0.06202591240416515</v>
       </c>
       <c r="Y10">
-        <v>-0.01361384351441519</v>
+        <v>-0.06463074086668102</v>
       </c>
       <c r="Z10">
-        <v>0.3287557846420106</v>
+        <v>0.293978748524203</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.08422823668299195</v>
+        <v>0.06148649614662758</v>
       </c>
       <c r="AC10">
-        <v>-0.08422823668299195</v>
+        <v>-0.06148649614662758</v>
       </c>
       <c r="AD10">
-        <v>2732.5</v>
+        <v>47.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>2732.5</v>
+        <v>47.2</v>
       </c>
       <c r="AG10">
-        <v>2013.6</v>
+        <v>19</v>
       </c>
       <c r="AH10">
-        <v>0.7491432488005483</v>
+        <v>0.08729424819678194</v>
       </c>
       <c r="AI10">
-        <v>0.6583226925578818</v>
+        <v>0.1767790262172285</v>
       </c>
       <c r="AJ10">
-        <v>0.6875640237656218</v>
+        <v>0.03707317073170732</v>
       </c>
       <c r="AK10">
-        <v>0.5867474794568448</v>
+        <v>0.07956448911222781</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1641,7 +1647,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT Victoria Investama Tbk (IDX:VICO)</t>
+          <t>PT Bank Oke Indonesia Tbk (IDX:DNAR)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1650,10 +1656,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0203</v>
+        <v>0.145</v>
       </c>
       <c r="E11">
-        <v>-0.462</v>
+        <v>-0.00967</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1668,10 +1674,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="L11">
-        <v>0.02395209580838323</v>
+        <v>0.06428571428571428</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1695,55 +1701,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>154.1</v>
+        <v>40</v>
       </c>
       <c r="V11">
-        <v>1.459280303030303</v>
+        <v>0.3014318010550113</v>
       </c>
       <c r="W11">
-        <v>0.01173881144534116</v>
+        <v>0.007634730538922155</v>
       </c>
       <c r="X11">
-        <v>0.09844063782373881</v>
+        <v>0.0645932023709257</v>
       </c>
       <c r="Y11">
-        <v>-0.08670182637839766</v>
+        <v>-0.05695847183200354</v>
       </c>
       <c r="Z11">
-        <v>0.4570865522125588</v>
+        <v>0.1313900850171138</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.08461719012440921</v>
+        <v>0.06195485730467885</v>
       </c>
       <c r="AC11">
-        <v>-0.08461719012440921</v>
+        <v>-0.06195485730467885</v>
       </c>
       <c r="AD11">
-        <v>98.40000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>98.40000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="AG11">
-        <v>-55.69999999999999</v>
+        <v>-7.100000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.4823529411764706</v>
+        <v>0.1986714975845411</v>
       </c>
       <c r="AI11">
-        <v>0.2900088417329797</v>
+        <v>0.1246684350132626</v>
       </c>
       <c r="AJ11">
-        <v>-1.116232464929859</v>
+        <v>-0.05652866242038218</v>
       </c>
       <c r="AK11">
-        <v>-0.3007559395248379</v>
+        <v>-0.03171058508262618</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1760,7 +1766,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PT Bank Victoria International Tbk (IDX:BVIC)</t>
+          <t>PT Bank Artha Graha Internasional Tbk (IDX:INPC)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1769,7 +1775,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0479</v>
+        <v>-0.00156</v>
+      </c>
+      <c r="E12">
+        <v>0.223</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1784,10 +1793,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>-2.85</v>
+        <v>6.46</v>
       </c>
       <c r="L12">
-        <v>-0.08482142857142858</v>
+        <v>0.09228571428571429</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1796,7 +1805,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1805,61 +1814,61 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>50.1</v>
+        <v>158.2</v>
       </c>
       <c r="V12">
-        <v>0.561030235162374</v>
+        <v>1.647916666666666</v>
       </c>
       <c r="W12">
-        <v>-0.01503164556962025</v>
+        <v>0.02454407294832827</v>
       </c>
       <c r="X12">
-        <v>0.1041707952444622</v>
+        <v>0.06557643159995537</v>
       </c>
       <c r="Y12">
-        <v>-0.1192024408140824</v>
+        <v>-0.0410323586516271</v>
       </c>
       <c r="Z12">
-        <v>0.1321793863099922</v>
+        <v>0.4006868918145393</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.08589399806603105</v>
+        <v>0.06223243557813019</v>
       </c>
       <c r="AC12">
-        <v>-0.08589399806603105</v>
+        <v>-0.06223243557813019</v>
       </c>
       <c r="AD12">
-        <v>101.3</v>
+        <v>29.4</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>101.3</v>
+        <v>29.4</v>
       </c>
       <c r="AG12">
-        <v>51.2</v>
+        <v>-128.8</v>
       </c>
       <c r="AH12">
-        <v>0.531479538300105</v>
+        <v>0.2344497607655502</v>
       </c>
       <c r="AI12">
-        <v>0.3159700561447286</v>
+        <v>0.09935789117945253</v>
       </c>
       <c r="AJ12">
-        <v>0.3644128113879003</v>
+        <v>3.926829268292685</v>
       </c>
       <c r="AK12">
-        <v>0.189279112754159</v>
+        <v>-0.9353667392883077</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1876,7 +1885,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PT Bank Woori Saudara Indonesia 1906 Tbk (IDX:SDRA)</t>
+          <t>PT Bank MNC Internasional Tbk (IDX:BABP)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1884,12 +1893,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.09470000000000001</v>
-      </c>
-      <c r="E13">
-        <v>0.156</v>
-      </c>
       <c r="G13">
         <v>0</v>
       </c>
@@ -1903,85 +1906,82 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>53.1</v>
+        <v>3.42</v>
       </c>
       <c r="L13">
-        <v>0.4187697160883281</v>
+        <v>0.07702702702702703</v>
       </c>
       <c r="M13">
-        <v>10.4</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.03326935380678183</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.1958568738229755</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>10.4</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.03326935380678183</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.1958568738229755</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>89</v>
+        <v>154.9</v>
       </c>
       <c r="V13">
-        <v>0.2847088931541906</v>
+        <v>1.188795088257866</v>
       </c>
       <c r="W13">
-        <v>0.08603370058327932</v>
+        <v>0.02179732313575526</v>
       </c>
       <c r="X13">
-        <v>0.1403861716242006</v>
+        <v>0.06667561644444117</v>
       </c>
       <c r="Y13">
-        <v>-0.05435247104092124</v>
+        <v>-0.04487829330868591</v>
       </c>
       <c r="Z13">
-        <v>0.1286525974025974</v>
+        <v>0.4852459016393442</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.08817535238004406</v>
+        <v>0.06374263831902778</v>
       </c>
       <c r="AC13">
-        <v>-0.08817535238004406</v>
+        <v>-0.06374263831902778</v>
       </c>
       <c r="AD13">
-        <v>754.8</v>
+        <v>48.4</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>754.8</v>
+        <v>48.4</v>
       </c>
       <c r="AG13">
-        <v>665.8</v>
+        <v>-106.5</v>
       </c>
       <c r="AH13">
-        <v>0.7071388420460932</v>
+        <v>0.2708449916060436</v>
       </c>
       <c r="AI13">
-        <v>0.543021582733813</v>
+        <v>0.1737257717157215</v>
       </c>
       <c r="AJ13">
-        <v>0.6804987735077678</v>
+        <v>-4.474789915966384</v>
       </c>
       <c r="AK13">
-        <v>0.5117601844734819</v>
+        <v>-0.8609539207760712</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PT Bank QNB Indonesia Tbk (IDX:BKSW)</t>
+          <t>PT Bank IBK Indonesia Tbk (IDX:AGRS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2006,8 +2006,26 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.385</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
       <c r="K14">
-        <v>-87.2</v>
+        <v>12.2</v>
+      </c>
+      <c r="L14">
+        <v>0.3495702005730659</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2016,7 +2034,7 @@
         <v>-0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2025,61 +2043,61 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>131.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="V14">
-        <v>0.9835082458770613</v>
+        <v>0.4781746031746032</v>
       </c>
       <c r="W14">
-        <v>-0.3560636994691711</v>
+        <v>0.06177215189873417</v>
       </c>
       <c r="X14">
-        <v>0.08601302667163108</v>
+        <v>0.0909194246401253</v>
       </c>
       <c r="Y14">
-        <v>-0.4420767261408022</v>
+        <v>-0.02914727274139112</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>0.07807606263982103</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.1074997460531805</v>
+        <v>0.06541037260064692</v>
       </c>
       <c r="AC14">
-        <v>-0.1074997460531805</v>
+        <v>-0.06541037260064692</v>
       </c>
       <c r="AD14">
-        <v>65.7</v>
+        <v>364.8</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>65.7</v>
+        <v>364.8</v>
       </c>
       <c r="AG14">
-        <v>-65.49999999999999</v>
+        <v>268.4</v>
       </c>
       <c r="AH14">
-        <v>0.3299849321948769</v>
+        <v>0.6440677966101696</v>
       </c>
       <c r="AI14">
-        <v>0.2142857142857143</v>
+        <v>0.5659323611542042</v>
       </c>
       <c r="AJ14">
-        <v>-0.9646539027982322</v>
+        <v>0.571063829787234</v>
       </c>
       <c r="AK14">
-        <v>-0.3734321550741161</v>
+        <v>0.4896023349142648</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2096,7 +2114,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PT Bank IBK Indonesia Tbk (IDX:AGRS)</t>
+          <t>PT Bank Tabungan Negara (Persero) Tbk (IDX:BBTN)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2105,10 +2123,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.213</v>
+        <v>0.0438</v>
       </c>
       <c r="E15">
-        <v>1.057</v>
+        <v>0.0498</v>
+      </c>
+      <c r="F15">
+        <v>0.135</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2123,87 +2144,453 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>5.57</v>
+        <v>199.3</v>
       </c>
       <c r="L15">
-        <v>0.2442982456140351</v>
+        <v>0.2519914022000253</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>39.4</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.03490123128709362</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.1976919217260411</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>39.4</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.03490123128709362</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.1976919217260411</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>91.09999999999999</v>
+        <v>1557.6</v>
       </c>
       <c r="V15">
-        <v>0.5758533501896334</v>
+        <v>1.379750199309062</v>
       </c>
       <c r="W15">
-        <v>0.0400431344356578</v>
+        <v>0.1405302496121845</v>
       </c>
       <c r="X15">
-        <v>0.1329853972474829</v>
+        <v>0.1034954308267163</v>
       </c>
       <c r="Y15">
-        <v>-0.09294226281182508</v>
+        <v>0.0370348187854682</v>
       </c>
       <c r="Z15">
-        <v>0.06490179333902649</v>
+        <v>0.2304621481438312</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.1087493128012946</v>
+        <v>0.06598974282594237</v>
       </c>
       <c r="AC15">
-        <v>-0.1087493128012946</v>
+        <v>-0.06598974282594237</v>
       </c>
       <c r="AD15">
-        <v>340.6</v>
+        <v>2884.9</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>340.6</v>
+        <v>2884.9</v>
       </c>
       <c r="AG15">
-        <v>249.5</v>
+        <v>1327.3</v>
       </c>
       <c r="AH15">
-        <v>0.6828388131515638</v>
+        <v>0.7187453286162738</v>
       </c>
       <c r="AI15">
-        <v>0.6329678498420368</v>
+        <v>0.605702408196687</v>
       </c>
       <c r="AJ15">
-        <v>0.6119695854795193</v>
+        <v>0.5403875905870857</v>
       </c>
       <c r="AK15">
-        <v>0.5581655480984341</v>
+        <v>0.4140954044863195</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PT Bank Woori Saudara Indonesia 1906 Tbk (IDX:SDRA)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.0701</v>
+      </c>
+      <c r="E16">
+        <v>0.0919</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>53.3</v>
+      </c>
+      <c r="L16">
+        <v>0.40625</v>
+      </c>
+      <c r="M16">
+        <v>12.8</v>
+      </c>
+      <c r="N16">
+        <v>0.04067365745154115</v>
+      </c>
+      <c r="O16">
+        <v>0.2401500938086304</v>
+      </c>
+      <c r="P16">
+        <v>12.8</v>
+      </c>
+      <c r="Q16">
+        <v>0.04067365745154115</v>
+      </c>
+      <c r="R16">
+        <v>0.2401500938086304</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>111.5</v>
+      </c>
+      <c r="V16">
+        <v>0.3543056879567842</v>
+      </c>
+      <c r="W16">
+        <v>0.08380503144654088</v>
+      </c>
+      <c r="X16">
+        <v>0.1044053337129816</v>
+      </c>
+      <c r="Y16">
+        <v>-0.0206003022664407</v>
+      </c>
+      <c r="Z16">
+        <v>0.1261174661155436</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.06602237138034751</v>
+      </c>
+      <c r="AC16">
+        <v>-0.06602237138034751</v>
+      </c>
+      <c r="AD16">
+        <v>821.2</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>821.2</v>
+      </c>
+      <c r="AG16">
+        <v>709.7</v>
+      </c>
+      <c r="AH16">
+        <v>0.7229509639933093</v>
+      </c>
+      <c r="AI16">
+        <v>0.549003877523733</v>
+      </c>
+      <c r="AJ16">
+        <v>0.6927957828973057</v>
+      </c>
+      <c r="AK16">
+        <v>0.5126778877410966</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PT Bank Victoria International Tbk (IDX:BVIC)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.09230000000000001</v>
+      </c>
+      <c r="E17">
+        <v>0.522</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>14.4</v>
+      </c>
+      <c r="L17">
+        <v>0.28125</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>-0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>41.2</v>
+      </c>
+      <c r="V17">
+        <v>0.407920792079208</v>
+      </c>
+      <c r="W17">
+        <v>0.06566347469220246</v>
+      </c>
+      <c r="X17">
+        <v>0.0856512320345557</v>
+      </c>
+      <c r="Y17">
+        <v>-0.01998775734235324</v>
+      </c>
+      <c r="Z17">
+        <v>0.189279112754159</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.06778264916556931</v>
+      </c>
+      <c r="AC17">
+        <v>-0.06778264916556931</v>
+      </c>
+      <c r="AD17">
+        <v>151.2</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>151.2</v>
+      </c>
+      <c r="AG17">
+        <v>110</v>
+      </c>
+      <c r="AH17">
+        <v>0.5995241871530531</v>
+      </c>
+      <c r="AI17">
+        <v>0.3791374122367102</v>
+      </c>
+      <c r="AJ17">
+        <v>0.5213270142180094</v>
+      </c>
+      <c r="AK17">
+        <v>0.3076062639821029</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PT Victoria Investama Tbk (IDX:VICO)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0509</v>
+      </c>
+      <c r="E18">
+        <v>0.338</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>7.57</v>
+      </c>
+      <c r="L18">
+        <v>0.1162826420890937</v>
+      </c>
+      <c r="M18">
+        <v>23.6</v>
+      </c>
+      <c r="N18">
+        <v>0.2005097706032286</v>
+      </c>
+      <c r="O18">
+        <v>3.117569352708058</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>-0</v>
+      </c>
+      <c r="S18">
+        <v>23.6</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>162.1</v>
+      </c>
+      <c r="V18">
+        <v>1.377230246389125</v>
+      </c>
+      <c r="W18">
+        <v>0.0534982332155477</v>
+      </c>
+      <c r="X18">
+        <v>0.08241410755514872</v>
+      </c>
+      <c r="Y18">
+        <v>-0.02891587433960102</v>
+      </c>
+      <c r="Z18">
+        <v>0.7617153220616625</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06855123330281808</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06855123330281808</v>
+      </c>
+      <c r="AD18">
+        <v>153.6</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>153.6</v>
+      </c>
+      <c r="AG18">
+        <v>-8.5</v>
+      </c>
+      <c r="AH18">
+        <v>0.5661629192775525</v>
+      </c>
+      <c r="AI18">
+        <v>0.3180124223602485</v>
+      </c>
+      <c r="AJ18">
+        <v>-0.07783882783882784</v>
+      </c>
+      <c r="AK18">
+        <v>-0.02648800249298847</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
         <v>0</v>
       </c>
     </row>
